--- a/artfynd/A 4451-2026 artfynd.xlsx
+++ b/artfynd/A 4451-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1796,6 +1796,3030 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131368554</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>635086</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6672291</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131372555</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>635525</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6672098</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131368114</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91814</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>635084</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6672255</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131373393</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91814</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>635688</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6672191</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131370781</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92196</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>635303</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6672152</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131369894</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>635324</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6672227</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131368139</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>635092</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6672257</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131368258</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91871</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>635092</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6672251</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131368580</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>635089</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6672270</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131373732</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>635709</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6672164</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131373099</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92468</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>635600</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6672076</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131373850</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>635780</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6672276</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131373655</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>635725</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6672185</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131378571</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Björklinge-Velången, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>635699</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6672197</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131372667</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91814</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>635505</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6672109</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131372686</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>635512</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6672114</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131372681</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92273</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>635512</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6672114</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131373921</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Björklinge-Velången, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>635721</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6672319</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131373146</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>635598</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6672076</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131374160</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>635718</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6672244</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131367906</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>635094</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6672237</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131372788</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>635528</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6672094</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131371350</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92536</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>635284</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6672176</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131373585</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91814</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>635725</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6672184</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131368305</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92468</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>635085</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6672251</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131370368</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Björklinge-Velången, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>635387</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6672168</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131370495</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91835</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>635390</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6672176</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131372539</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>635496</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6672082</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4451-2026 artfynd.xlsx
+++ b/artfynd/A 4451-2026 artfynd.xlsx
@@ -1798,32 +1798,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131368554</v>
+        <v>131368114</v>
       </c>
       <c r="B11" t="n">
-        <v>5197</v>
+        <v>91816</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635086</v>
+        <v>635084</v>
       </c>
       <c r="R11" t="n">
-        <v>6672291</v>
+        <v>6672255</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1895,27 +1895,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131372555</v>
+        <v>131368554</v>
       </c>
       <c r="B12" t="n">
-        <v>57881</v>
+        <v>5197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1923,32 +1923,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>635525</v>
+        <v>635086</v>
       </c>
       <c r="R12" t="n">
-        <v>6672098</v>
+        <v>6672291</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1957,7 +1945,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Uppsala</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1967,7 +1955,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Viksta</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1975,19 +1963,9 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2014,10 +1992,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131368114</v>
+        <v>131372555</v>
       </c>
       <c r="B13" t="n">
-        <v>91814</v>
+        <v>57883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,37 +2003,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>635084</v>
+        <v>635525</v>
       </c>
       <c r="R13" t="n">
-        <v>6672255</v>
+        <v>6672098</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2064,7 +2054,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2074,7 +2064,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Viksta</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2082,9 +2072,19 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2111,45 +2111,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131373393</v>
+        <v>131370781</v>
       </c>
       <c r="B14" t="n">
-        <v>91814</v>
+        <v>92198</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1506</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635688</v>
+        <v>635303</v>
       </c>
       <c r="R14" t="n">
-        <v>6672191</v>
+        <v>6672152</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Viksta</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2218,45 +2218,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131370781</v>
+        <v>131373393</v>
       </c>
       <c r="B15" t="n">
-        <v>92196</v>
+        <v>91816</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635303</v>
+        <v>635688</v>
       </c>
       <c r="R15" t="n">
-        <v>6672152</v>
+        <v>6672191</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Uppsala</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Viksta</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2325,45 +2325,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131369894</v>
+        <v>131368258</v>
       </c>
       <c r="B16" t="n">
-        <v>57881</v>
+        <v>91873</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635324</v>
+        <v>635092</v>
       </c>
       <c r="R16" t="n">
-        <v>6672227</v>
+        <v>6672251</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,7 +2378,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2385,7 +2388,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Viksta</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2393,19 +2396,14 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:47</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,8 +2412,24 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2435,7 +2449,7 @@
         <v>131368139</v>
       </c>
       <c r="B17" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,48 +2552,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131368258</v>
+        <v>131369894</v>
       </c>
       <c r="B18" t="n">
-        <v>91871</v>
+        <v>57883</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5321</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635092</v>
+        <v>635324</v>
       </c>
       <c r="R18" t="n">
-        <v>6672251</v>
+        <v>6672227</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2602,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Uppsala</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2601,7 +2612,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Viksta</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2609,14 +2620,19 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2625,24 +2641,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2662,7 +2662,7 @@
         <v>131368580</v>
       </c>
       <c r="B19" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,53 +2756,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131373732</v>
+        <v>131373099</v>
       </c>
       <c r="B20" t="n">
-        <v>57881</v>
+        <v>92470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635709</v>
+        <v>635600</v>
       </c>
       <c r="R20" t="n">
-        <v>6672164</v>
+        <v>6672076</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2831,7 +2826,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,7 +2836,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2868,48 +2863,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131373099</v>
+        <v>131373732</v>
       </c>
       <c r="B21" t="n">
-        <v>92468</v>
+        <v>57883</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635600</v>
+        <v>635709</v>
       </c>
       <c r="R21" t="n">
-        <v>6672076</v>
+        <v>6672164</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,7 +2978,7 @@
         <v>131373850</v>
       </c>
       <c r="B22" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>131372667</v>
       </c>
       <c r="B25" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>131372686</v>
       </c>
       <c r="B26" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>131372681</v>
       </c>
       <c r="B27" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>131373921</v>
       </c>
       <c r="B28" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3738,10 +3738,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131373146</v>
+        <v>131374160</v>
       </c>
       <c r="B29" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3778,13 +3778,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635598</v>
+        <v>635718</v>
       </c>
       <c r="R29" t="n">
-        <v>6672076</v>
+        <v>6672244</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3850,10 +3850,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131374160</v>
+        <v>131373146</v>
       </c>
       <c r="B30" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,13 +3890,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635718</v>
+        <v>635598</v>
       </c>
       <c r="R30" t="n">
-        <v>6672244</v>
+        <v>6672076</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3962,10 +3962,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131367906</v>
+        <v>131372788</v>
       </c>
       <c r="B31" t="n">
-        <v>58043</v>
+        <v>57883</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3973,21 +3973,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4001,17 +4001,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635094</v>
+        <v>635528</v>
       </c>
       <c r="R31" t="n">
-        <v>6672237</v>
+        <v>6672094</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4038,9 +4038,19 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4067,10 +4077,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131372788</v>
+        <v>131367906</v>
       </c>
       <c r="B32" t="n">
-        <v>57881</v>
+        <v>58045</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4078,21 +4088,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4106,17 +4116,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635528</v>
+        <v>635094</v>
       </c>
       <c r="R32" t="n">
-        <v>6672094</v>
+        <v>6672237</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4143,19 +4153,9 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4185,7 +4185,7 @@
         <v>131371350</v>
       </c>
       <c r="B33" t="n">
-        <v>92536</v>
+        <v>92538</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>131373585</v>
       </c>
       <c r="B34" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>131368305</v>
       </c>
       <c r="B35" t="n">
-        <v>92468</v>
+        <v>92470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>131370368</v>
       </c>
       <c r="B36" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>131370495</v>
       </c>
       <c r="B37" t="n">
-        <v>91835</v>
+        <v>91837</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>131372539</v>
       </c>
       <c r="B38" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 4451-2026 artfynd.xlsx
+++ b/artfynd/A 4451-2026 artfynd.xlsx
@@ -1798,10 +1798,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131368114</v>
+        <v>131372555</v>
       </c>
       <c r="B11" t="n">
-        <v>91816</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,37 +1809,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635084</v>
+        <v>635525</v>
       </c>
       <c r="R11" t="n">
-        <v>6672255</v>
+        <v>6672098</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1848,7 +1860,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1858,7 +1870,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Viksta</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1866,9 +1878,19 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1992,10 +2014,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131372555</v>
+        <v>131368114</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>91817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2003,49 +2025,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>635525</v>
+        <v>635084</v>
       </c>
       <c r="R13" t="n">
-        <v>6672098</v>
+        <v>6672255</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2054,7 +2064,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Uppsala</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2064,7 +2074,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Viksta</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2072,19 +2082,9 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2114,7 +2114,7 @@
         <v>131370781</v>
       </c>
       <c r="B14" t="n">
-        <v>92198</v>
+        <v>92199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>131373393</v>
       </c>
       <c r="B15" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2325,38 +2325,44 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131368258</v>
+        <v>131368139</v>
       </c>
       <c r="B16" t="n">
-        <v>91873</v>
+        <v>57884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5321</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
@@ -2366,7 +2372,7 @@
         <v>635092</v>
       </c>
       <c r="R16" t="n">
-        <v>6672251</v>
+        <v>6672257</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2401,35 +2407,14 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2446,10 +2431,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131368139</v>
+        <v>131369894</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2474,26 +2459,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635092</v>
+        <v>635324</v>
       </c>
       <c r="R17" t="n">
-        <v>6672257</v>
+        <v>6672227</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2505,7 +2481,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Uppsala</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2515,7 +2491,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Viksta</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2523,9 +2499,19 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,45 +2538,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131369894</v>
+        <v>131368258</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
+        <v>91874</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635324</v>
+        <v>635092</v>
       </c>
       <c r="R18" t="n">
-        <v>6672227</v>
+        <v>6672251</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2602,7 +2591,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2612,7 +2601,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Viksta</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2620,19 +2609,14 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:47</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2641,8 +2625,24 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2662,7 +2662,7 @@
         <v>131368580</v>
       </c>
       <c r="B19" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,48 +2756,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131373099</v>
+        <v>131373732</v>
       </c>
       <c r="B20" t="n">
-        <v>92470</v>
+        <v>57884</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635600</v>
+        <v>635709</v>
       </c>
       <c r="R20" t="n">
-        <v>6672076</v>
+        <v>6672164</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2826,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2836,7 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2863,53 +2868,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131373732</v>
+        <v>131373099</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>92471</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635709</v>
+        <v>635600</v>
       </c>
       <c r="R21" t="n">
-        <v>6672164</v>
+        <v>6672076</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,7 +2978,7 @@
         <v>131373850</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>131372667</v>
       </c>
       <c r="B25" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>131372686</v>
       </c>
       <c r="B26" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>131372681</v>
       </c>
       <c r="B27" t="n">
-        <v>92275</v>
+        <v>92276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>131373921</v>
       </c>
       <c r="B28" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3738,10 +3738,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131374160</v>
+        <v>131373146</v>
       </c>
       <c r="B29" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3778,13 +3778,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635718</v>
+        <v>635598</v>
       </c>
       <c r="R29" t="n">
-        <v>6672244</v>
+        <v>6672076</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3850,10 +3850,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131373146</v>
+        <v>131374160</v>
       </c>
       <c r="B30" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,13 +3890,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635598</v>
+        <v>635718</v>
       </c>
       <c r="R30" t="n">
-        <v>6672076</v>
+        <v>6672244</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3965,7 +3965,7 @@
         <v>131372788</v>
       </c>
       <c r="B31" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>131367906</v>
       </c>
       <c r="B32" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>131371350</v>
       </c>
       <c r="B33" t="n">
-        <v>92538</v>
+        <v>92539</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>131373585</v>
       </c>
       <c r="B34" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>131368305</v>
       </c>
       <c r="B35" t="n">
-        <v>92470</v>
+        <v>92471</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>131370368</v>
       </c>
       <c r="B36" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>131370495</v>
       </c>
       <c r="B37" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>131372539</v>
       </c>
       <c r="B38" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 4451-2026 artfynd.xlsx
+++ b/artfynd/A 4451-2026 artfynd.xlsx
@@ -1798,10 +1798,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131372555</v>
+        <v>131368114</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>91817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,49 +1809,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635525</v>
+        <v>635084</v>
       </c>
       <c r="R11" t="n">
-        <v>6672098</v>
+        <v>6672255</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1860,7 +1848,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Uppsala</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1870,7 +1858,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Viksta</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1878,19 +1866,9 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1917,27 +1895,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131368554</v>
+        <v>131372555</v>
       </c>
       <c r="B12" t="n">
-        <v>5197</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1945,20 +1923,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>635086</v>
+        <v>635525</v>
       </c>
       <c r="R12" t="n">
-        <v>6672291</v>
+        <v>6672098</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1967,7 +1957,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1977,7 +1967,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Viksta</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1985,9 +1975,19 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2014,32 +2014,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131368114</v>
+        <v>131368554</v>
       </c>
       <c r="B13" t="n">
-        <v>91817</v>
+        <v>5197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>635084</v>
+        <v>635086</v>
       </c>
       <c r="R13" t="n">
-        <v>6672255</v>
+        <v>6672291</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2111,45 +2111,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131370781</v>
+        <v>131373393</v>
       </c>
       <c r="B14" t="n">
-        <v>92199</v>
+        <v>91817</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635303</v>
+        <v>635688</v>
       </c>
       <c r="R14" t="n">
-        <v>6672152</v>
+        <v>6672191</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Uppsala</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Viksta</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2218,45 +2218,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131373393</v>
+        <v>131370781</v>
       </c>
       <c r="B15" t="n">
-        <v>91817</v>
+        <v>92199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1506</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635688</v>
+        <v>635303</v>
       </c>
       <c r="R15" t="n">
-        <v>6672191</v>
+        <v>6672152</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Viksta</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2756,53 +2756,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131373732</v>
+        <v>131373099</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>92471</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635709</v>
+        <v>635600</v>
       </c>
       <c r="R20" t="n">
-        <v>6672164</v>
+        <v>6672076</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2831,7 +2826,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,7 +2836,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2868,48 +2863,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131373099</v>
+        <v>131373732</v>
       </c>
       <c r="B21" t="n">
-        <v>92471</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635600</v>
+        <v>635709</v>
       </c>
       <c r="R21" t="n">
-        <v>6672076</v>
+        <v>6672164</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3404,43 +3404,35 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131372686</v>
+        <v>131372681</v>
       </c>
       <c r="B26" t="n">
-        <v>58046</v>
+        <v>92276</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
@@ -3453,7 +3445,7 @@
         <v>6672114</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3519,35 +3511,43 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131372681</v>
+        <v>131372686</v>
       </c>
       <c r="B27" t="n">
-        <v>92276</v>
+        <v>58046</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
@@ -3560,7 +3560,7 @@
         <v>6672114</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131373146</v>
+        <v>131374160</v>
       </c>
       <c r="B29" t="n">
         <v>57884</v>
@@ -3778,13 +3778,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635598</v>
+        <v>635718</v>
       </c>
       <c r="R29" t="n">
-        <v>6672076</v>
+        <v>6672244</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3850,7 +3850,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131374160</v>
+        <v>131373146</v>
       </c>
       <c r="B30" t="n">
         <v>57884</v>
@@ -3890,13 +3890,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635718</v>
+        <v>635598</v>
       </c>
       <c r="R30" t="n">
-        <v>6672244</v>
+        <v>6672076</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3962,10 +3962,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131372788</v>
+        <v>131367906</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>58046</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3973,21 +3973,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4001,17 +4001,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635528</v>
+        <v>635094</v>
       </c>
       <c r="R31" t="n">
-        <v>6672094</v>
+        <v>6672237</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4038,19 +4038,9 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4077,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131367906</v>
+        <v>131372788</v>
       </c>
       <c r="B32" t="n">
-        <v>58046</v>
+        <v>57884</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4088,21 +4078,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4116,17 +4106,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635094</v>
+        <v>635528</v>
       </c>
       <c r="R32" t="n">
-        <v>6672237</v>
+        <v>6672094</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4153,9 +4143,19 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4289,45 +4289,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131373585</v>
+        <v>131368305</v>
       </c>
       <c r="B34" t="n">
-        <v>91817</v>
+        <v>92471</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635725</v>
+        <v>635085</v>
       </c>
       <c r="R34" t="n">
-        <v>6672184</v>
+        <v>6672251</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4357,19 +4357,9 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4396,45 +4386,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131368305</v>
+        <v>131373585</v>
       </c>
       <c r="B35" t="n">
-        <v>92471</v>
+        <v>91817</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635085</v>
+        <v>635725</v>
       </c>
       <c r="R35" t="n">
-        <v>6672251</v>
+        <v>6672184</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4464,9 +4454,19 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 4451-2026 artfynd.xlsx
+++ b/artfynd/A 4451-2026 artfynd.xlsx
@@ -2111,45 +2111,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131373393</v>
+        <v>131370781</v>
       </c>
       <c r="B14" t="n">
-        <v>91817</v>
+        <v>92199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1506</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635688</v>
+        <v>635303</v>
       </c>
       <c r="R14" t="n">
-        <v>6672191</v>
+        <v>6672152</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Viksta</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2218,45 +2218,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131370781</v>
+        <v>131373393</v>
       </c>
       <c r="B15" t="n">
-        <v>92199</v>
+        <v>91817</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635303</v>
+        <v>635688</v>
       </c>
       <c r="R15" t="n">
-        <v>6672152</v>
+        <v>6672191</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Uppsala</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Viksta</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2325,44 +2325,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131368139</v>
+        <v>131368258</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>91874</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
@@ -2372,7 +2366,7 @@
         <v>635092</v>
       </c>
       <c r="R16" t="n">
-        <v>6672257</v>
+        <v>6672251</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2407,14 +2401,35 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2538,38 +2553,44 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131368258</v>
+        <v>131368139</v>
       </c>
       <c r="B18" t="n">
-        <v>91874</v>
+        <v>57884</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5321</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
@@ -2579,7 +2600,7 @@
         <v>635092</v>
       </c>
       <c r="R18" t="n">
-        <v>6672251</v>
+        <v>6672257</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2614,35 +2635,14 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2756,48 +2756,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131373099</v>
+        <v>131373732</v>
       </c>
       <c r="B20" t="n">
-        <v>92471</v>
+        <v>57884</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635600</v>
+        <v>635709</v>
       </c>
       <c r="R20" t="n">
-        <v>6672076</v>
+        <v>6672164</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2826,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2836,7 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2863,53 +2868,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131373732</v>
+        <v>131373099</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>92471</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635709</v>
+        <v>635600</v>
       </c>
       <c r="R21" t="n">
-        <v>6672164</v>
+        <v>6672076</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3738,7 +3738,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131374160</v>
+        <v>131373146</v>
       </c>
       <c r="B29" t="n">
         <v>57884</v>
@@ -3778,13 +3778,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635718</v>
+        <v>635598</v>
       </c>
       <c r="R29" t="n">
-        <v>6672244</v>
+        <v>6672076</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3850,7 +3850,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131373146</v>
+        <v>131374160</v>
       </c>
       <c r="B30" t="n">
         <v>57884</v>
@@ -3890,13 +3890,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635598</v>
+        <v>635718</v>
       </c>
       <c r="R30" t="n">
-        <v>6672076</v>
+        <v>6672244</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4289,45 +4289,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131368305</v>
+        <v>131373585</v>
       </c>
       <c r="B34" t="n">
-        <v>92471</v>
+        <v>91817</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635085</v>
+        <v>635725</v>
       </c>
       <c r="R34" t="n">
-        <v>6672251</v>
+        <v>6672184</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4357,9 +4357,19 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4386,45 +4396,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131373585</v>
+        <v>131368305</v>
       </c>
       <c r="B35" t="n">
-        <v>91817</v>
+        <v>92471</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635725</v>
+        <v>635085</v>
       </c>
       <c r="R35" t="n">
-        <v>6672184</v>
+        <v>6672251</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4454,19 +4464,9 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 4451-2026 artfynd.xlsx
+++ b/artfynd/A 4451-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68540736</v>
+        <v>131368114</v>
       </c>
       <c r="B2" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>söder om Annedal, Upl</t>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635524.912874074</v>
+        <v>635084</v>
       </c>
       <c r="R2" t="n">
-        <v>6672112.772144717</v>
+        <v>6672255</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -735,7 +725,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Uppsala</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -745,27 +735,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Viksta</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,81 +756,61 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>äldre blandskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>murken björk med fnöskticka</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68540730</v>
+        <v>131372249</v>
       </c>
       <c r="B3" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>söder om Annedal, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635304.5347035254</v>
+        <v>635417</v>
       </c>
       <c r="R3" t="n">
-        <v>6672147.969429119</v>
+        <v>6672098</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +822,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Uppsala</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -872,27 +832,27 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Viksta</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,79 +863,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>äldre blandskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>torrgran</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68540733</v>
+        <v>131372667</v>
       </c>
       <c r="B4" t="n">
-        <v>88806</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5685</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>söder om Annedal, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635316.781500305</v>
+        <v>635505</v>
       </c>
       <c r="R4" t="n">
-        <v>6672208.205543042</v>
+        <v>6672109</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +929,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -994,27 +939,27 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Viksta</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,76 +970,61 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>äldre blandskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>låga</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68540708</v>
+        <v>131373393</v>
       </c>
       <c r="B5" t="n">
-        <v>88806</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5685</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SO om Annedal, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635823.2473145406</v>
+        <v>635688</v>
       </c>
       <c r="R5" t="n">
-        <v>6672263.318035566</v>
+        <v>6672191</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,22 +1051,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,84 +1077,64 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>äldre blandskog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68540732</v>
+        <v>131373585</v>
       </c>
       <c r="B6" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>söder om Annedal, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635275.3752920163</v>
+        <v>635725</v>
       </c>
       <c r="R6" t="n">
-        <v>6672167.318705051</v>
+        <v>6672184</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1248,22 +1158,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,76 +1184,61 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>äldre blandskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>68540707</v>
+        <v>131372197</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>SO om Annedal, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635717.0058219095</v>
+        <v>635404</v>
       </c>
       <c r="R7" t="n">
-        <v>6672194.614707712</v>
+        <v>6672108</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1250,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1365,27 +1260,27 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Viksta</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,76 +1291,61 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>äldre blandskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>68540731</v>
+        <v>131372681</v>
       </c>
       <c r="B8" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>söder om Annedal, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>635290.5440696133</v>
+        <v>635512</v>
       </c>
       <c r="R8" t="n">
-        <v>6672148.449093063</v>
+        <v>6672114</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,22 +1372,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,84 +1398,64 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>äldre blandskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>68540709</v>
+        <v>131368305</v>
       </c>
       <c r="B9" t="n">
-        <v>5112</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102204</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SO om Annedal, Upl</t>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635704.1218077948</v>
+        <v>635085</v>
       </c>
       <c r="R9" t="n">
-        <v>6672178.693141835</v>
+        <v>6672251</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,22 +1479,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1645,81 +1495,61 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>äldre blandskog</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>spärrgrenig gran</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>68540737</v>
+        <v>131373099</v>
       </c>
       <c r="B10" t="n">
-        <v>6203</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101520</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Större flatbagge</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Peltis grossa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>söder om Annedal, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635522.5471482022</v>
+        <v>635600</v>
       </c>
       <c r="R10" t="n">
-        <v>6672082.293742798</v>
+        <v>6672076</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,22 +1576,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,58 +1602,48 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>äldre blandskog</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>granhögstubbe</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131368554</v>
+        <v>131370781</v>
       </c>
       <c r="B11" t="n">
-        <v>5198</v>
+        <v>92292</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>1506</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1833,13 +1653,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635086</v>
+        <v>635303</v>
       </c>
       <c r="R11" t="n">
-        <v>6672291</v>
+        <v>6672152</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1848,7 +1668,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1858,7 +1678,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Viksta</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1866,9 +1686,19 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,32 +1725,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131368114</v>
+        <v>131371350</v>
       </c>
       <c r="B12" t="n">
-        <v>91838</v>
+        <v>92632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1930,13 +1760,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>635084</v>
+        <v>635284</v>
       </c>
       <c r="R12" t="n">
-        <v>6672255</v>
+        <v>6672176</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1963,9 +1793,19 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1992,57 +1832,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131372555</v>
+        <v>131368258</v>
       </c>
       <c r="B13" t="n">
-        <v>57901</v>
+        <v>91966</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>635525</v>
+        <v>635092</v>
       </c>
       <c r="R13" t="n">
-        <v>6672098</v>
+        <v>6672251</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2072,19 +1903,14 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:30</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2093,8 +1919,24 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2111,45 +1953,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131370781</v>
+        <v>131370495</v>
       </c>
       <c r="B14" t="n">
-        <v>92221</v>
+        <v>91930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1506</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635303</v>
+        <v>635390</v>
       </c>
       <c r="R14" t="n">
-        <v>6672152</v>
+        <v>6672176</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2181,7 +2023,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2191,7 +2033,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2218,45 +2060,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131373393</v>
+        <v>68540708</v>
       </c>
       <c r="B15" t="n">
-        <v>91838</v>
+        <v>91282</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5685</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>SO om Annedal, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635688</v>
+        <v>635823</v>
       </c>
       <c r="R15" t="n">
-        <v>6672191</v>
+        <v>6672263</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2283,22 +2125,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,61 +2141,71 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131369894</v>
+        <v>68540733</v>
       </c>
       <c r="B16" t="n">
-        <v>57901</v>
+        <v>91282</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>söder om Annedal, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635324</v>
+        <v>635317</v>
       </c>
       <c r="R16" t="n">
-        <v>6672227</v>
+        <v>6672208</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2390,22 +2232,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2416,16 +2248,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>låga</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2435,11 +2277,11 @@
         <v>131368139</v>
       </c>
       <c r="B17" t="n">
-        <v>57901</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2538,10 +2380,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131368258</v>
+        <v>131368580</v>
       </c>
       <c r="B18" t="n">
-        <v>91895</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2549,37 +2391,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5321</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635092</v>
+        <v>635089</v>
       </c>
       <c r="R18" t="n">
-        <v>6672251</v>
+        <v>6672270</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2430,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Uppsala</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2601,7 +2440,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Viksta</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2614,35 +2453,14 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2659,14 +2477,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131368580</v>
+        <v>131369894</v>
       </c>
       <c r="B19" t="n">
-        <v>57901</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2690,14 +2508,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635089</v>
+        <v>635324</v>
       </c>
       <c r="R19" t="n">
-        <v>6672270</v>
+        <v>6672227</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2727,9 +2545,19 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2756,10 +2584,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131373099</v>
+        <v>131370368</v>
       </c>
       <c r="B20" t="n">
-        <v>92493</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2767,34 +2595,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>Nyckelmyrsröret, Björklinge-Velången, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635600</v>
+        <v>635387</v>
       </c>
       <c r="R20" t="n">
-        <v>6672076</v>
+        <v>6672168</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2806,7 +2634,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2816,7 +2644,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Viksta</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2826,7 +2654,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2836,7 +2664,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2863,14 +2691,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131373732</v>
+        <v>131372555</v>
       </c>
       <c r="B21" t="n">
-        <v>57901</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2891,25 +2719,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635709</v>
+        <v>635525</v>
       </c>
       <c r="R21" t="n">
-        <v>6672164</v>
+        <v>6672098</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2918,7 +2753,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2928,7 +2763,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Viksta</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2938,7 +2773,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2948,7 +2783,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,14 +2810,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131373850</v>
+        <v>131372788</v>
       </c>
       <c r="B22" t="n">
-        <v>57901</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3004,21 +2839,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635780</v>
+        <v>635528</v>
       </c>
       <c r="R22" t="n">
-        <v>6672276</v>
+        <v>6672094</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3030,7 +2868,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -3040,7 +2878,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Viksta</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3050,7 +2888,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3060,7 +2898,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3087,10 +2925,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131373655</v>
+        <v>131373146</v>
       </c>
       <c r="B23" t="n">
-        <v>5198</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3098,16 +2936,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3116,16 +2954,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635725</v>
+        <v>635598</v>
       </c>
       <c r="R23" t="n">
-        <v>6672185</v>
+        <v>6672076</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3157,7 +3000,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3167,7 +3010,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3194,10 +3037,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131378571</v>
+        <v>131373732</v>
       </c>
       <c r="B24" t="n">
-        <v>5178</v>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3205,42 +3048,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Björklinge-Velången, Upl</t>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635699</v>
+        <v>635709</v>
       </c>
       <c r="R24" t="n">
-        <v>6672197</v>
+        <v>6672164</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3267,18 +3110,27 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3297,45 +3149,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131372667</v>
+        <v>131373850</v>
       </c>
       <c r="B25" t="n">
-        <v>91838</v>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635505</v>
+        <v>635780</v>
       </c>
       <c r="R25" t="n">
-        <v>6672109</v>
+        <v>6672276</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3347,7 +3204,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Uppsala</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3357,7 +3214,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Viksta</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3367,7 +3224,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3377,7 +3234,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3404,45 +3261,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131372681</v>
+        <v>131373921</v>
       </c>
       <c r="B26" t="n">
-        <v>92298</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>Nyckelmyrsröret, Björklinge-Velången, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635512</v>
+        <v>635721</v>
       </c>
       <c r="R26" t="n">
-        <v>6672114</v>
+        <v>6672319</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3454,7 +3316,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Uppsala</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3464,7 +3326,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Viksta</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3474,7 +3336,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3484,7 +3346,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3511,53 +3373,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131372686</v>
+        <v>131374160</v>
       </c>
       <c r="B27" t="n">
-        <v>58063</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635512</v>
+        <v>635718</v>
       </c>
       <c r="R27" t="n">
-        <v>6672114</v>
+        <v>6672244</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3569,7 +3428,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Uppsala</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3579,7 +3438,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Viksta</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3589,7 +3448,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3599,7 +3458,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3626,50 +3485,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131373921</v>
+        <v>68540730</v>
       </c>
       <c r="B28" t="n">
-        <v>57901</v>
+        <v>5179</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Björklinge-Velången, Upl</t>
+          <t>söder om Annedal, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635721</v>
+        <v>635305</v>
       </c>
       <c r="R28" t="n">
-        <v>6672319</v>
+        <v>6672148</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3681,7 +3540,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3691,27 +3550,17 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Viksta</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:28</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:28</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3722,66 +3571,76 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131373146</v>
+        <v>68540735</v>
       </c>
       <c r="B29" t="n">
-        <v>57901</v>
+        <v>5179</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>söder om Annedal, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635598</v>
+        <v>635405</v>
       </c>
       <c r="R29" t="n">
-        <v>6672076</v>
+        <v>6672194</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3793,7 +3652,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3803,27 +3662,17 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Viksta</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3834,69 +3683,79 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131374160</v>
+        <v>131378571</v>
       </c>
       <c r="B30" t="n">
-        <v>57901</v>
+        <v>5179</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>Nyckelmyrsröret, Björklinge-Velången, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635718</v>
+        <v>635699</v>
       </c>
       <c r="R30" t="n">
-        <v>6672244</v>
+        <v>6672197</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3923,27 +3782,18 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3962,10 +3812,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131367906</v>
+        <v>68540734</v>
       </c>
       <c r="B31" t="n">
-        <v>58063</v>
+        <v>6275</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3973,42 +3823,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>101520</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Större flatbagge</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Peltis grossa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+          <t>söder om Annedal, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635094</v>
+        <v>635388</v>
       </c>
       <c r="R31" t="n">
-        <v>6672237</v>
+        <v>6672224</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4035,12 +3882,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4051,26 +3898,36 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>björkhögstubbe</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131372788</v>
+        <v>68540737</v>
       </c>
       <c r="B32" t="n">
-        <v>57901</v>
+        <v>6275</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4078,16 +3935,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>101520</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Större flatbagge</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Peltis grossa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4096,27 +3953,24 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>söder om Annedal, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635528</v>
+        <v>635523</v>
       </c>
       <c r="R32" t="n">
-        <v>6672094</v>
+        <v>6672082</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4125,7 +3979,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Uppsala</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -4135,27 +3989,17 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Viksta</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4166,26 +4010,36 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>granhögstubbe</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131371350</v>
+        <v>68540736</v>
       </c>
       <c r="B33" t="n">
-        <v>92561</v>
+        <v>44177</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4193,34 +4047,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3298</v>
+        <v>101735</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+          <t>söder om Annedal, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635284</v>
+        <v>635525</v>
       </c>
       <c r="R33" t="n">
-        <v>6672176</v>
+        <v>6672113</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4232,7 +4091,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -4242,27 +4101,17 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Viksta</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4273,26 +4122,36 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>murken björk med fnöskticka</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131373585</v>
+        <v>68540709</v>
       </c>
       <c r="B34" t="n">
-        <v>91838</v>
+        <v>5178</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4300,37 +4159,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>102204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>SO om Annedal, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635725</v>
+        <v>635704</v>
       </c>
       <c r="R34" t="n">
-        <v>6672184</v>
+        <v>6672179</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4354,22 +4218,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4380,26 +4234,36 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>spärrgrenig gran</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131368305</v>
+        <v>68540731</v>
       </c>
       <c r="B35" t="n">
-        <v>92493</v>
+        <v>4781</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4407,37 +4271,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+          <t>söder om Annedal, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635085</v>
+        <v>635291</v>
       </c>
       <c r="R35" t="n">
-        <v>6672251</v>
+        <v>6672148</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4446,7 +4315,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4456,17 +4325,17 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Viksta</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4477,61 +4346,76 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131370368</v>
+        <v>68540732</v>
       </c>
       <c r="B36" t="n">
-        <v>57901</v>
+        <v>4781</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Björklinge-Velången, Upl</t>
+          <t>söder om Annedal, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635387</v>
+        <v>635275</v>
       </c>
       <c r="R36" t="n">
-        <v>6672168</v>
+        <v>6672167</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4543,7 +4427,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Uppsala</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4553,27 +4437,17 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Viksta</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:04</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:04</t>
+          <t>2017-12-03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4584,26 +4458,36 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131370495</v>
+        <v>131367906</v>
       </c>
       <c r="B37" t="n">
-        <v>91859</v>
+        <v>58114</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4611,34 +4495,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>635390</v>
+        <v>635094</v>
       </c>
       <c r="R37" t="n">
-        <v>6672176</v>
+        <v>6672237</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4668,19 +4560,9 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4710,7 +4592,7 @@
         <v>131372539</v>
       </c>
       <c r="B38" t="n">
-        <v>58063</v>
+        <v>58114</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4819,6 +4701,427 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131372686</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>635512</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6672114</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131368554</v>
+      </c>
+      <c r="B40" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Götbrunnabotten, Götbrunnabotten, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>635086</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6672291</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131373655</v>
+      </c>
+      <c r="B41" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Nyckelmyrsröret, Nyckelmyrsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>635725</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6672185</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>68540707</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SO om Annedal, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>635717</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6672195</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2017-12-03</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2017-12-03</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
